--- a/外部验证_validation_predictions.xlsx
+++ b/外部验证_validation_predictions.xlsx
@@ -442,7 +442,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -547,12 +547,12 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -567,7 +567,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -582,7 +582,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -717,7 +717,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -792,7 +792,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -872,7 +872,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -922,12 +922,12 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -947,12 +947,12 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -977,7 +977,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -997,7 +997,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -1007,7 +1007,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
